--- a/gym_members.xlsx
+++ b/gym_members.xlsx
@@ -520,7 +520,11 @@
       <c r="J2" t="n">
         <v>2194673957</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Okay</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
